--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/100.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/100.xlsx
@@ -426,13 +426,13 @@
         <v>-13.69096454592256</v>
       </c>
       <c r="E2">
-        <v>-10.4118197019292</v>
+        <v>-7.692289921362847</v>
       </c>
       <c r="F2">
-        <v>-1.119742491775721</v>
+        <v>-1.844352088178843</v>
       </c>
       <c r="G2">
-        <v>-11.37747880621211</v>
+        <v>-9.72416587953577</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.56171268606467</v>
       </c>
       <c r="E3">
-        <v>-10.41249444455635</v>
+        <v>-7.31729604573568</v>
       </c>
       <c r="F3">
-        <v>-1.168618031885055</v>
+        <v>-1.169587259905304</v>
       </c>
       <c r="G3">
-        <v>-10.57323473617481</v>
+        <v>-8.614560399501627</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.38475115149264</v>
       </c>
       <c r="E4">
-        <v>-11.27089839202832</v>
+        <v>-8.29530604869824</v>
       </c>
       <c r="F4">
-        <v>-1.420821615212872</v>
+        <v>-1.497283728663246</v>
       </c>
       <c r="G4">
-        <v>-10.03112959357361</v>
+        <v>-8.990721136401318</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.3396798961596</v>
       </c>
       <c r="E5">
-        <v>-12.72974629359932</v>
+        <v>-9.92529856844113</v>
       </c>
       <c r="F5">
-        <v>-1.270161295918244</v>
+        <v>-1.361861827686977</v>
       </c>
       <c r="G5">
-        <v>-9.425120990427864</v>
+        <v>-8.659544092289245</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.410363109469657</v>
       </c>
       <c r="E6">
-        <v>-13.46232659076817</v>
+        <v>-11.02824464080131</v>
       </c>
       <c r="F6">
-        <v>-1.148552477936438</v>
+        <v>-1.504674092317644</v>
       </c>
       <c r="G6">
-        <v>-9.237694454722027</v>
+        <v>-7.225200579216914</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.6149219880253</v>
       </c>
       <c r="E7">
-        <v>-12.44268179777909</v>
+        <v>-10.37040680712906</v>
       </c>
       <c r="F7">
-        <v>-1.227703724031228</v>
+        <v>-1.205284783092267</v>
       </c>
       <c r="G7">
-        <v>-9.246060203299765</v>
+        <v>-8.180835896765092</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.917620591354432</v>
       </c>
       <c r="E8">
-        <v>-14.72727429227875</v>
+        <v>-12.47913601354084</v>
       </c>
       <c r="F8">
-        <v>-0.9369527387216152</v>
+        <v>-1.107993769442033</v>
       </c>
       <c r="G8">
-        <v>-8.32179892582726</v>
+        <v>-6.982958030471823</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.293449056639015</v>
       </c>
       <c r="E9">
-        <v>-15.0573909904899</v>
+        <v>-12.6071695591597</v>
       </c>
       <c r="F9">
-        <v>-0.9880003314939749</v>
+        <v>-0.8850412343723834</v>
       </c>
       <c r="G9">
-        <v>-8.059607029662521</v>
+        <v>-6.308537003757037</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.695691889776659</v>
       </c>
       <c r="E10">
-        <v>-15.66976747359915</v>
+        <v>-12.65374491432859</v>
       </c>
       <c r="F10">
-        <v>-0.8109491368244642</v>
+        <v>-1.687216787248941</v>
       </c>
       <c r="G10">
-        <v>-7.175052435388034</v>
+        <v>-5.458018128171798</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.08771469757693</v>
       </c>
       <c r="E11">
-        <v>-16.23351720281403</v>
+        <v>-14.62280239692179</v>
       </c>
       <c r="F11">
-        <v>-0.932207163946001</v>
+        <v>-1.295642332244707</v>
       </c>
       <c r="G11">
-        <v>-5.958191900972585</v>
+        <v>-5.3086562450765</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.432724819863052</v>
       </c>
       <c r="E12">
-        <v>-16.86967270293756</v>
+        <v>-13.61807439731398</v>
       </c>
       <c r="F12">
-        <v>-0.8338899088625623</v>
+        <v>-0.9601278992351984</v>
       </c>
       <c r="G12">
-        <v>-6.311314551464485</v>
+        <v>-3.582974792911686</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.702738237050701</v>
       </c>
       <c r="E13">
-        <v>-16.84999648337423</v>
+        <v>-15.99426886404079</v>
       </c>
       <c r="F13">
-        <v>-0.9488922976181132</v>
+        <v>-1.152598054697428</v>
       </c>
       <c r="G13">
-        <v>-5.142880677197494</v>
+        <v>-3.439495749239673</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.884437393376517</v>
       </c>
       <c r="E14">
-        <v>-18.65882297015403</v>
+        <v>-16.45298969559578</v>
       </c>
       <c r="F14">
-        <v>-0.6976357704277295</v>
+        <v>-1.177383052274055</v>
       </c>
       <c r="G14">
-        <v>-4.443037971286644</v>
+        <v>-2.567703308019077</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.974020825944846</v>
       </c>
       <c r="E15">
-        <v>-19.49079421484323</v>
+        <v>-17.68609769635842</v>
       </c>
       <c r="F15">
-        <v>-0.6181614483261894</v>
+        <v>-1.303678847912605</v>
       </c>
       <c r="G15">
-        <v>-2.999712948166271</v>
+        <v>-1.454045720244868</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.986549389358625</v>
       </c>
       <c r="E16">
-        <v>-19.81561259846541</v>
+        <v>-17.3945500112706</v>
       </c>
       <c r="F16">
-        <v>-0.6341695477194513</v>
+        <v>-1.100778405291291</v>
       </c>
       <c r="G16">
-        <v>-3.283761065981278</v>
+        <v>-0.7071105040378846</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.9562993085214186</v>
       </c>
       <c r="E17">
-        <v>-21.00158371328221</v>
+        <v>-19.90089734945186</v>
       </c>
       <c r="F17">
-        <v>-0.5923692137873425</v>
+        <v>-0.8990570317240224</v>
       </c>
       <c r="G17">
-        <v>-2.816172992923537</v>
+        <v>-1.169666547875933</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.06713253488482293</v>
       </c>
       <c r="E18">
-        <v>-20.45539540626907</v>
+        <v>-19.09696641581816</v>
       </c>
       <c r="F18">
-        <v>-0.4063677051367258</v>
+        <v>-0.9601017680875936</v>
       </c>
       <c r="G18">
-        <v>-3.011697123018432</v>
+        <v>-0.7890200217705323</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.019655544184119</v>
       </c>
       <c r="E19">
-        <v>-22.445541992316</v>
+        <v>-20.14570212583251</v>
       </c>
       <c r="F19">
-        <v>-0.2763145672137961</v>
+        <v>-0.5306878276457647</v>
       </c>
       <c r="G19">
-        <v>-1.782696818110475</v>
+        <v>1.415472252830151</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.835058775588069</v>
       </c>
       <c r="E20">
-        <v>-22.76726742819094</v>
+        <v>-20.04750216697618</v>
       </c>
       <c r="F20">
-        <v>-0.2537332964185027</v>
+        <v>-0.5082015792053977</v>
       </c>
       <c r="G20">
-        <v>-1.774576049902643</v>
+        <v>0.2912937513321378</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.45448507976025</v>
       </c>
       <c r="E21">
-        <v>-24.07610057130985</v>
+        <v>-21.02608728613772</v>
       </c>
       <c r="F21">
-        <v>-0.02004006783034242</v>
+        <v>-0.6440011940424994</v>
       </c>
       <c r="G21">
-        <v>-1.276709727342728</v>
+        <v>0.3297523588618512</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>2.837315988676802</v>
       </c>
       <c r="E22">
-        <v>-23.73109425056147</v>
+        <v>-22.49317701040268</v>
       </c>
       <c r="F22">
-        <v>0.07080367903813745</v>
+        <v>-0.804686371781859</v>
       </c>
       <c r="G22">
-        <v>-1.460792612053902</v>
+        <v>1.285669072780867</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.96967080389172</v>
       </c>
       <c r="E23">
-        <v>-23.9112958167487</v>
+        <v>-22.13812200583129</v>
       </c>
       <c r="F23">
-        <v>-0.1238527824403559</v>
+        <v>-0.7006543139025571</v>
       </c>
       <c r="G23">
-        <v>-1.501790408012237</v>
+        <v>0.5040062338669294</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.861132502665545</v>
       </c>
       <c r="E24">
-        <v>-23.72176106563166</v>
+        <v>-23.37791856270326</v>
       </c>
       <c r="F24">
-        <v>-0.06853631037292918</v>
+        <v>-0.7388176671998592</v>
       </c>
       <c r="G24">
-        <v>-1.627832808328909</v>
+        <v>0.4372424619764474</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.542685207252561</v>
       </c>
       <c r="E25">
-        <v>-24.21049662290949</v>
+        <v>-23.01578555325788</v>
       </c>
       <c r="F25">
-        <v>-0.2790607132711681</v>
+        <v>-0.6632693520626934</v>
       </c>
       <c r="G25">
-        <v>-1.36909381116163</v>
+        <v>0.5443386101718702</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.058961776397174</v>
       </c>
       <c r="E26">
-        <v>-24.42270997185694</v>
+        <v>-24.48878946457686</v>
       </c>
       <c r="F26">
-        <v>-0.03880856663421531</v>
+        <v>-0.7366844153317622</v>
       </c>
       <c r="G26">
-        <v>-1.880616134071039</v>
+        <v>1.117476806658195</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.461888875975695</v>
       </c>
       <c r="E27">
-        <v>-24.99061231173685</v>
+        <v>-21.71035329411873</v>
       </c>
       <c r="F27">
-        <v>-0.09052923442063679</v>
+        <v>-0.4839566253459352</v>
       </c>
       <c r="G27">
-        <v>-1.54356287162676</v>
+        <v>0.6230071038215715</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.8048934703462348</v>
       </c>
       <c r="E28">
-        <v>-24.12043433184494</v>
+        <v>-22.62331629643511</v>
       </c>
       <c r="F28">
-        <v>-0.3494992012721684</v>
+        <v>-0.8456172511663914</v>
       </c>
       <c r="G28">
-        <v>-1.353236298028521</v>
+        <v>-0.7345549265584427</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.1346214986862004</v>
       </c>
       <c r="E29">
-        <v>-25.02745144778925</v>
+        <v>-22.48023010321475</v>
       </c>
       <c r="F29">
-        <v>0.04525137594547968</v>
+        <v>-0.735925028345309</v>
       </c>
       <c r="G29">
-        <v>-0.5511209087729655</v>
+        <v>0.4775748382813882</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.5117031430694661</v>
       </c>
       <c r="E30">
-        <v>-23.90763228127649</v>
+        <v>-22.81686780399695</v>
       </c>
       <c r="F30">
-        <v>-0.02442534951019425</v>
+        <v>-1.012558859124695</v>
       </c>
       <c r="G30">
-        <v>-1.814855457478956</v>
+        <v>0.7410148101144323</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.108180226840921</v>
       </c>
       <c r="E31">
-        <v>-24.12629870568487</v>
+        <v>-23.25819023841446</v>
       </c>
       <c r="F31">
-        <v>-0.1262608072847816</v>
+        <v>-0.8598793147878814</v>
       </c>
       <c r="G31">
-        <v>-1.89845997452771</v>
+        <v>-0.6626035298079227</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.64108109708526</v>
       </c>
       <c r="E32">
-        <v>-24.37755655752645</v>
+        <v>-21.92316440163519</v>
       </c>
       <c r="F32">
-        <v>-0.3259273224267676</v>
+        <v>-0.7849272649278787</v>
       </c>
       <c r="G32">
-        <v>-2.201676151015098</v>
+        <v>0.4213816382977991</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.108639024234397</v>
       </c>
       <c r="E33">
-        <v>-22.60580468744745</v>
+        <v>-21.2001799408886</v>
       </c>
       <c r="F33">
-        <v>-0.4857161226179884</v>
+        <v>-0.305013693960432</v>
       </c>
       <c r="G33">
-        <v>-2.319667304580262</v>
+        <v>0.01952444692228755</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.51894132905135</v>
       </c>
       <c r="E34">
-        <v>-23.20726754819821</v>
+        <v>-21.41924034253564</v>
       </c>
       <c r="F34">
-        <v>-0.04678015035957977</v>
+        <v>-0.5379340740618579</v>
       </c>
       <c r="G34">
-        <v>-2.509811798173842</v>
+        <v>-1.250933819773963</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.886340912098456</v>
       </c>
       <c r="E35">
-        <v>-22.40891116606795</v>
+        <v>-20.73209875355976</v>
       </c>
       <c r="F35">
-        <v>-0.2397032457136247</v>
+        <v>-0.5568894501637526</v>
       </c>
       <c r="G35">
-        <v>-2.078371571859403</v>
+        <v>0.2753667167427041</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.227954133070063</v>
       </c>
       <c r="E36">
-        <v>-21.33083094448389</v>
+        <v>-20.9077627887913</v>
       </c>
       <c r="F36">
-        <v>-0.1061319050995462</v>
+        <v>-0.4266035074712533</v>
       </c>
       <c r="G36">
-        <v>-2.189341058335773</v>
+        <v>-0.5692196612361611</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.559745944588059</v>
       </c>
       <c r="E37">
-        <v>-21.40272952630367</v>
+        <v>-19.89957956351563</v>
       </c>
       <c r="F37">
-        <v>0.2008979933148686</v>
+        <v>-0.2396248522708104</v>
       </c>
       <c r="G37">
-        <v>-2.251652146475935</v>
+        <v>-0.7835576216307348</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.892113732540313</v>
       </c>
       <c r="E38">
-        <v>-21.23698284914893</v>
+        <v>-20.05590701473442</v>
       </c>
       <c r="F38">
-        <v>0.3080119429056156</v>
+        <v>-0.2456207628666641</v>
       </c>
       <c r="G38">
-        <v>-1.954613447964828</v>
+        <v>-0.3883049686060693</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.230954433090726</v>
       </c>
       <c r="E39">
-        <v>-21.08928214091475</v>
+        <v>-19.04549125177297</v>
       </c>
       <c r="F39">
-        <v>0.2437776228283493</v>
+        <v>-0.1511455783340816</v>
       </c>
       <c r="G39">
-        <v>-2.272607899739522</v>
+        <v>-0.8578959217150693</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.576521587820135</v>
       </c>
       <c r="E40">
-        <v>-19.48385206418947</v>
+        <v>-17.91128965181185</v>
       </c>
       <c r="F40">
-        <v>0.4223024558521765</v>
+        <v>0.3559142957299126</v>
       </c>
       <c r="G40">
-        <v>-2.789149009686466</v>
+        <v>-1.06375226443803</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.923623443488439</v>
       </c>
       <c r="E41">
-        <v>-19.5760291526156</v>
+        <v>-17.7012590273361</v>
       </c>
       <c r="F41">
-        <v>0.4729770858814502</v>
+        <v>-0.09746111521251524</v>
       </c>
       <c r="G41">
-        <v>-2.632639658771882</v>
+        <v>-1.180829707434356</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.265334613977741</v>
       </c>
       <c r="E42">
-        <v>-19.05582070098447</v>
+        <v>-17.70719132828615</v>
       </c>
       <c r="F42">
-        <v>0.4865945811953563</v>
+        <v>0.4248783535236387</v>
       </c>
       <c r="G42">
-        <v>-2.485479288460199</v>
+        <v>-1.18139912126711</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.593595302469241</v>
       </c>
       <c r="E43">
-        <v>-18.80987474915388</v>
+        <v>-17.86039866091365</v>
       </c>
       <c r="F43">
-        <v>0.669923586113669</v>
+        <v>0.1703451387942108</v>
       </c>
       <c r="G43">
-        <v>-3.747085156384438</v>
+        <v>-1.645266141138711</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.903719746318654</v>
       </c>
       <c r="E44">
-        <v>-18.29621447093784</v>
+        <v>-16.19609389361464</v>
       </c>
       <c r="F44">
-        <v>0.7975370250738643</v>
+        <v>0.2076239923377399</v>
       </c>
       <c r="G44">
-        <v>-3.670724112975608</v>
+        <v>-1.492818829600812</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.195334905076044</v>
       </c>
       <c r="E45">
-        <v>-17.64041445056904</v>
+        <v>-16.06751240264085</v>
       </c>
       <c r="F45">
-        <v>0.3552253836566964</v>
+        <v>0.07356487030170612</v>
       </c>
       <c r="G45">
-        <v>-3.930347025801872</v>
+        <v>-2.358225228476154</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.471213739052989</v>
       </c>
       <c r="E46">
-        <v>-17.89250101315403</v>
+        <v>-14.45232799290304</v>
       </c>
       <c r="F46">
-        <v>0.6104696823421567</v>
+        <v>0.5873744989773032</v>
       </c>
       <c r="G46">
-        <v>-3.900419694126861</v>
+        <v>-2.227306394580135</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.738233459904365</v>
       </c>
       <c r="E47">
-        <v>-16.72638725686086</v>
+        <v>-14.61363223705626</v>
       </c>
       <c r="F47">
-        <v>0.7751592604887049</v>
+        <v>0.459631196132042</v>
       </c>
       <c r="G47">
-        <v>-4.440214075941646</v>
+        <v>-2.168375373435569</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.003607109360177</v>
       </c>
       <c r="E48">
-        <v>-17.31471754298937</v>
+        <v>-14.35929049441545</v>
       </c>
       <c r="F48">
-        <v>0.7980849873206063</v>
+        <v>0.5872192957975901</v>
       </c>
       <c r="G48">
-        <v>-4.636714816970627</v>
+        <v>-2.80630094612543</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.276865788904453</v>
       </c>
       <c r="E49">
-        <v>-15.24241085302129</v>
+        <v>-14.04936173333049</v>
       </c>
       <c r="F49">
-        <v>0.7791533668074432</v>
+        <v>0.4122720544367408</v>
       </c>
       <c r="G49">
-        <v>-4.424747207182171</v>
+        <v>-3.437847097561116</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.568053390536567</v>
       </c>
       <c r="E50">
-        <v>-15.98955925107281</v>
+        <v>-13.08661721624779</v>
       </c>
       <c r="F50">
-        <v>0.6934701256644227</v>
+        <v>0.2889362051541475</v>
       </c>
       <c r="G50">
-        <v>-4.579313267865204</v>
+        <v>-3.382200137591507</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.882647253958996</v>
       </c>
       <c r="E51">
-        <v>-14.740411395375</v>
+        <v>-13.63563129104172</v>
       </c>
       <c r="F51">
-        <v>0.6032970782511314</v>
+        <v>0.3784528064654891</v>
       </c>
       <c r="G51">
-        <v>-5.184341949531327</v>
+        <v>-3.255114915429964</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.221978459844051</v>
       </c>
       <c r="E52">
-        <v>-13.79952582232732</v>
+        <v>-12.58003494290574</v>
       </c>
       <c r="F52">
-        <v>0.697017626915007</v>
+        <v>0.9927652043878312</v>
       </c>
       <c r="G52">
-        <v>-5.066930141435535</v>
+        <v>-3.682258053634429</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.58253340708532</v>
       </c>
       <c r="E53">
-        <v>-14.32712927201298</v>
+        <v>-12.07709356266585</v>
       </c>
       <c r="F53">
-        <v>0.8173634394292507</v>
+        <v>0.6124477310305406</v>
       </c>
       <c r="G53">
-        <v>-5.260173305653873</v>
+        <v>-3.854035640576133</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.961322574768392</v>
       </c>
       <c r="E54">
-        <v>-13.32525421103</v>
+        <v>-11.47635525775632</v>
       </c>
       <c r="F54">
-        <v>0.7614158605545214</v>
+        <v>0.3280640353539522</v>
       </c>
       <c r="G54">
-        <v>-5.66396054507878</v>
+        <v>-4.715250888798757</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.356618808371682</v>
       </c>
       <c r="E55">
-        <v>-14.16087087729537</v>
+        <v>-10.42979774373966</v>
       </c>
       <c r="F55">
-        <v>0.3872178268544887</v>
+        <v>0.5597625863416165</v>
       </c>
       <c r="G55">
-        <v>-5.361052249326544</v>
+        <v>-5.233258570419598</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.761250248442838</v>
       </c>
       <c r="E56">
-        <v>-13.2503940072092</v>
+        <v>-11.42641524639973</v>
       </c>
       <c r="F56">
-        <v>0.5135635092293747</v>
+        <v>0.4247009784611095</v>
       </c>
       <c r="G56">
-        <v>-5.879225458224349</v>
+        <v>-4.438932894817948</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.16801709111144</v>
       </c>
       <c r="E57">
-        <v>-12.92082525435297</v>
+        <v>-9.844465307404215</v>
       </c>
       <c r="F57">
-        <v>0.4465307807995268</v>
+        <v>0.2693125051559372</v>
       </c>
       <c r="G57">
-        <v>-5.923206055713567</v>
+        <v>-4.40771445038262</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.56591701310957</v>
       </c>
       <c r="E58">
-        <v>-12.43799482718115</v>
+        <v>-9.869113791427965</v>
       </c>
       <c r="F58">
-        <v>0.7107119319658119</v>
+        <v>0.05722736007803278</v>
       </c>
       <c r="G58">
-        <v>-5.580134221478894</v>
+        <v>-4.772308141168096</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.94443862931536</v>
       </c>
       <c r="E59">
-        <v>-12.47831183127144</v>
+        <v>-7.679098476578504</v>
       </c>
       <c r="F59">
-        <v>0.5410020060673207</v>
+        <v>0.2099140310914653</v>
       </c>
       <c r="G59">
-        <v>-6.357973380294974</v>
+        <v>-5.683873476497496</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.29562948377355</v>
       </c>
       <c r="E60">
-        <v>-11.2084869632546</v>
+        <v>-9.622651593560505</v>
       </c>
       <c r="F60">
-        <v>0.5232146130780626</v>
+        <v>0.5526850046055176</v>
       </c>
       <c r="G60">
-        <v>-6.475941360041363</v>
+        <v>-4.785047120403211</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.60921737164448</v>
       </c>
       <c r="E61">
-        <v>-11.76556172178218</v>
+        <v>-9.792392384790013</v>
       </c>
       <c r="F61">
-        <v>0.3820731581881837</v>
+        <v>-0.04911532473189523</v>
       </c>
       <c r="G61">
-        <v>-6.733352828447394</v>
+        <v>-5.266883781461975</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.87704206527158</v>
       </c>
       <c r="E62">
-        <v>-12.25916991709226</v>
+        <v>-9.762105950626713</v>
       </c>
       <c r="F62">
-        <v>0.8157733986901494</v>
+        <v>0.347519070672168</v>
       </c>
       <c r="G62">
-        <v>-6.446689379656362</v>
+        <v>-5.674968108996856</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.09263130778151</v>
       </c>
       <c r="E63">
-        <v>-11.99494251569271</v>
+        <v>-8.691117319338668</v>
       </c>
       <c r="F63">
-        <v>0.1840861631695211</v>
+        <v>0.2975183075099138</v>
       </c>
       <c r="G63">
-        <v>-6.760287426954904</v>
+        <v>-5.844633567884505</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.2544683883623</v>
       </c>
       <c r="E64">
-        <v>-11.57646170416988</v>
+        <v>-8.749471235401508</v>
       </c>
       <c r="F64">
-        <v>0.2450873476204178</v>
+        <v>0.3265278406159759</v>
       </c>
       <c r="G64">
-        <v>-7.05924293133325</v>
+        <v>-6.377359934972946</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.36904018365562</v>
       </c>
       <c r="E65">
-        <v>-10.93021223548326</v>
+        <v>-7.494449948915745</v>
       </c>
       <c r="F65">
-        <v>0.407245371861136</v>
+        <v>0.2282177122091568</v>
       </c>
       <c r="G65">
-        <v>-7.080072883866344</v>
+        <v>-6.595852630019304</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.44232840839208</v>
       </c>
       <c r="E66">
-        <v>-12.52237388336607</v>
+        <v>-8.054549728080445</v>
       </c>
       <c r="F66">
-        <v>0.03490344149399833</v>
+        <v>-0.02481494116539235</v>
       </c>
       <c r="G66">
-        <v>-7.046805211742208</v>
+        <v>-6.563690680105285</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.48041462750885</v>
       </c>
       <c r="E67">
-        <v>-10.9298227867186</v>
+        <v>-7.732326160064661</v>
       </c>
       <c r="F67">
-        <v>-0.02711764956644131</v>
+        <v>-0.2513323982506965</v>
       </c>
       <c r="G67">
-        <v>-7.181544415190545</v>
+        <v>-6.877735651051628</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.48503690363221</v>
       </c>
       <c r="E68">
-        <v>-10.76727321221327</v>
+        <v>-7.881018604106517</v>
       </c>
       <c r="F68">
-        <v>0.2758753824695183</v>
+        <v>-0.05957570230337279</v>
       </c>
       <c r="G68">
-        <v>-7.739265401100483</v>
+        <v>-6.644322327259774</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.45487960675663</v>
       </c>
       <c r="E69">
-        <v>-11.14118478255261</v>
+        <v>-6.677934386014726</v>
       </c>
       <c r="F69">
-        <v>-0.01058217610333804</v>
+        <v>-0.4041837746793348</v>
       </c>
       <c r="G69">
-        <v>-7.279231992963359</v>
+        <v>-6.856200552318669</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.39172435291189</v>
       </c>
       <c r="E70">
-        <v>-11.76591494275478</v>
+        <v>-7.324387636031692</v>
       </c>
       <c r="F70">
-        <v>0.1971770762665436</v>
+        <v>-0.06260612357256616</v>
       </c>
       <c r="G70">
-        <v>-7.352494365747431</v>
+        <v>-6.447159477122939</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.2944487526094</v>
       </c>
       <c r="E71">
-        <v>-10.98193646559887</v>
+        <v>-7.934345914020843</v>
       </c>
       <c r="F71">
-        <v>0.03509190249793562</v>
+        <v>0.3462077621741842</v>
       </c>
       <c r="G71">
-        <v>-7.706169877344389</v>
+        <v>-7.100148032016484</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-12.16380106101517</v>
       </c>
       <c r="E72">
-        <v>-12.15972009940981</v>
+        <v>-8.40316977108694</v>
       </c>
       <c r="F72">
-        <v>0.2131519178355813</v>
+        <v>0.08024969297077603</v>
       </c>
       <c r="G72">
-        <v>-8.057031425232967</v>
+        <v>-6.885316800336559</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-12.00066338198768</v>
       </c>
       <c r="E73">
-        <v>-11.56638132102881</v>
+        <v>-8.370945150048357</v>
       </c>
       <c r="F73">
-        <v>0.2687471221441254</v>
+        <v>0.1345312132224631</v>
       </c>
       <c r="G73">
-        <v>-7.601530153939105</v>
+        <v>-7.113757684728428</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.8075119900571</v>
       </c>
       <c r="E74">
-        <v>-11.46562730283215</v>
+        <v>-8.544027955095526</v>
       </c>
       <c r="F74">
-        <v>-0.1250255166707388</v>
+        <v>-0.2574518379079546</v>
       </c>
       <c r="G74">
-        <v>-8.624425825208656</v>
+        <v>-7.181580831191477</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.59311433558375</v>
       </c>
       <c r="E75">
-        <v>-12.20607355935232</v>
+        <v>-9.290012535327079</v>
       </c>
       <c r="F75">
-        <v>0.17256787004653</v>
+        <v>-0.2706639045075082</v>
       </c>
       <c r="G75">
-        <v>-8.506742552378643</v>
+        <v>-7.073087632778481</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.3631512278647</v>
       </c>
       <c r="E76">
-        <v>-12.42848050329104</v>
+        <v>-8.088667251254233</v>
       </c>
       <c r="F76">
-        <v>-0.174588385147374</v>
+        <v>-0.2496972218930053</v>
       </c>
       <c r="G76">
-        <v>-8.293599698923748</v>
+        <v>-7.118683776490863</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.12218492103612</v>
       </c>
       <c r="E77">
-        <v>-12.94746173846609</v>
+        <v>-9.135356091017121</v>
       </c>
       <c r="F77">
-        <v>-0.3317482335189653</v>
+        <v>-0.4771593595568691</v>
       </c>
       <c r="G77">
-        <v>-8.13128365113328</v>
+        <v>-6.357158986092313</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.87219051726949</v>
       </c>
       <c r="E78">
-        <v>-13.33652105436108</v>
+        <v>-9.688332580567756</v>
       </c>
       <c r="F78">
-        <v>0.04235161041431005</v>
+        <v>-0.2091250518983198</v>
       </c>
       <c r="G78">
-        <v>-8.090100464624747</v>
+        <v>-7.482823922537459</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.61232056581476</v>
       </c>
       <c r="E79">
-        <v>-14.32366951787112</v>
+        <v>-9.496465665336771</v>
       </c>
       <c r="F79">
-        <v>-0.1536019062089282</v>
+        <v>-0.1104340422188375</v>
       </c>
       <c r="G79">
-        <v>-8.239273646624307</v>
+        <v>-6.460434764735417</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.34556844016586</v>
       </c>
       <c r="E80">
-        <v>-14.71134312071976</v>
+        <v>-11.38787793259446</v>
       </c>
       <c r="F80">
-        <v>-0.1320326234936007</v>
+        <v>-0.0395426143260215</v>
       </c>
       <c r="G80">
-        <v>-8.639187547768266</v>
+        <v>-6.528784287939209</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.06996002439376</v>
       </c>
       <c r="E81">
-        <v>-14.90493538454767</v>
+        <v>-11.49589562309942</v>
       </c>
       <c r="F81">
-        <v>0.08236077295605682</v>
+        <v>-0.4361920549362814</v>
       </c>
       <c r="G81">
-        <v>-8.257004928532643</v>
+        <v>-6.548919025909057</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.782871912405723</v>
       </c>
       <c r="E82">
-        <v>-15.35328148215108</v>
+        <v>-13.02907389703232</v>
       </c>
       <c r="F82">
-        <v>-0.3179525712895723</v>
+        <v>-0.2899193928803787</v>
       </c>
       <c r="G82">
-        <v>-7.571675654265958</v>
+        <v>-6.747627900812732</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.481197015936024</v>
       </c>
       <c r="E83">
-        <v>-15.68880064985339</v>
+        <v>-12.95882367975133</v>
       </c>
       <c r="F83">
-        <v>0.1604343071753907</v>
+        <v>-0.5132836914880429</v>
       </c>
       <c r="G83">
-        <v>-7.396630558876994</v>
+        <v>-6.509920799456443</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.161667975506537</v>
       </c>
       <c r="E84">
-        <v>-16.51690457774004</v>
+        <v>-15.26330523209268</v>
       </c>
       <c r="F84">
-        <v>0.1050315231355725</v>
+        <v>-0.3281936055917615</v>
       </c>
       <c r="G84">
-        <v>-8.095781360770136</v>
+        <v>-6.077335124385415</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.828280595024744</v>
       </c>
       <c r="E85">
-        <v>-18.90911625703198</v>
+        <v>-14.67193633990501</v>
       </c>
       <c r="F85">
-        <v>-0.1134462508700033</v>
+        <v>0.02873490695336168</v>
       </c>
       <c r="G85">
-        <v>-7.457650534256841</v>
+        <v>-6.511592624953774</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.483744353433604</v>
       </c>
       <c r="E86">
-        <v>-19.77557183128959</v>
+        <v>-16.13452476100636</v>
       </c>
       <c r="F86">
-        <v>0.1653319177188872</v>
+        <v>-0.243270543288152</v>
       </c>
       <c r="G86">
-        <v>-6.946098416437578</v>
+        <v>-5.551623803294691</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.132280424764746</v>
       </c>
       <c r="E87">
-        <v>-19.97945278806292</v>
+        <v>-16.90831870011901</v>
       </c>
       <c r="F87">
-        <v>-0.1265514173202647</v>
+        <v>-0.256328990413908</v>
       </c>
       <c r="G87">
-        <v>-7.395465246847171</v>
+        <v>-6.289630478182259</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.778644717828873</v>
       </c>
       <c r="E88">
-        <v>-21.63902530002391</v>
+        <v>-17.94310218171574</v>
       </c>
       <c r="F88">
-        <v>-0.06634129397413011</v>
+        <v>-0.6037600185841407</v>
       </c>
       <c r="G88">
-        <v>-6.647235607334332</v>
+        <v>-5.212090942241498</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.426135893902424</v>
       </c>
       <c r="E89">
-        <v>-23.41689966696129</v>
+        <v>-20.98392719312631</v>
       </c>
       <c r="F89">
-        <v>0.2462094032615066</v>
+        <v>-0.4365856058562682</v>
       </c>
       <c r="G89">
-        <v>-7.430100174279025</v>
+        <v>-5.189228314747291</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.083412970852844</v>
       </c>
       <c r="E90">
-        <v>-24.17391108140152</v>
+        <v>-20.44430064495028</v>
       </c>
       <c r="F90">
-        <v>0.2405405279371911</v>
+        <v>-0.1258118266577545</v>
       </c>
       <c r="G90">
-        <v>-6.578995332133336</v>
+        <v>-5.324301883295095</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.75611597861468</v>
       </c>
       <c r="E91">
-        <v>-27.06692217272772</v>
+        <v>-22.64513901267808</v>
       </c>
       <c r="F91">
-        <v>0.1075131903050661</v>
+        <v>0.1406775758802836</v>
       </c>
       <c r="G91">
-        <v>-6.947786794662607</v>
+        <v>-5.104385653666849</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.449452495325499</v>
       </c>
       <c r="E92">
-        <v>-28.01084635183454</v>
+        <v>-24.31440245901549</v>
       </c>
       <c r="F92">
-        <v>0.2790301246530737</v>
+        <v>0.1344837020449999</v>
       </c>
       <c r="G92">
-        <v>-6.775320614248735</v>
+        <v>-5.249291542466288</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.165843757791023</v>
       </c>
       <c r="E93">
-        <v>-29.52815685284457</v>
+        <v>-27.38826268831201</v>
       </c>
       <c r="F93">
-        <v>-0.01083556904980835</v>
+        <v>-0.1316620363093878</v>
       </c>
       <c r="G93">
-        <v>-6.404930158223996</v>
+        <v>-4.665764854077731</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.903003447189373</v>
       </c>
       <c r="E94">
-        <v>-32.35827423291524</v>
+        <v>-29.3538332459193</v>
       </c>
       <c r="F94">
-        <v>-0.156538096976153</v>
+        <v>0.1073358152425369</v>
       </c>
       <c r="G94">
-        <v>-6.338341845247095</v>
+        <v>-5.341976885929264</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.662104423697262</v>
       </c>
       <c r="E95">
-        <v>-34.52741328258934</v>
+        <v>-31.70476109192032</v>
       </c>
       <c r="F95">
-        <v>0.03031623730992797</v>
+        <v>-0.03776886370072931</v>
       </c>
       <c r="G95">
-        <v>-5.959833931560063</v>
+        <v>-4.995932181800325</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.435412258462741</v>
       </c>
       <c r="E96">
-        <v>-36.46399707807355</v>
+        <v>-34.538426531376</v>
       </c>
       <c r="F96">
-        <v>0.2889773815079489</v>
+        <v>-0.1355436995081299</v>
       </c>
       <c r="G96">
-        <v>-6.321083971350874</v>
+        <v>-5.199689638651388</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.215756258427303</v>
       </c>
       <c r="E97">
-        <v>-38.81436339329761</v>
+        <v>-36.70752029631002</v>
       </c>
       <c r="F97">
-        <v>-0.08256002625414549</v>
+        <v>-0.1354906453599627</v>
       </c>
       <c r="G97">
-        <v>-7.057501584379593</v>
+        <v>-5.317554991486061</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.985167317906691</v>
       </c>
       <c r="E98">
-        <v>-41.6159196878019</v>
+        <v>-38.03583946308394</v>
       </c>
       <c r="F98">
-        <v>-0.1710590965148172</v>
+        <v>-0.0384427305677488</v>
       </c>
       <c r="G98">
-        <v>-6.214964434089537</v>
+        <v>-5.327304548099214</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.738540795913778</v>
       </c>
       <c r="E99">
-        <v>-43.88105785796461</v>
+        <v>-42.08121812785303</v>
       </c>
       <c r="F99">
-        <v>-0.1405996806431704</v>
+        <v>-0.3178995171414051</v>
       </c>
       <c r="G99">
-        <v>-6.697473135892773</v>
+        <v>-4.842289763322749</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.459002822747919</v>
       </c>
       <c r="E100">
-        <v>-46.90930503281887</v>
+        <v>-43.70590780453293</v>
       </c>
       <c r="F100">
-        <v>-0.1460990994345338</v>
+        <v>-0.1401546592809319</v>
       </c>
       <c r="G100">
-        <v>-6.770603086855274</v>
+        <v>-6.381633849264144</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.16715858325454</v>
       </c>
       <c r="E101">
-        <v>-48.45699480170936</v>
+        <v>-47.33144032286589</v>
       </c>
       <c r="F101">
-        <v>-0.4595905179839416</v>
+        <v>-0.6732538260065815</v>
       </c>
       <c r="G101">
-        <v>-6.016424397008365</v>
+        <v>-5.497989655012958</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.837076055365734</v>
       </c>
       <c r="E102">
-        <v>-50.96136206463077</v>
+        <v>-49.0142257925902</v>
       </c>
       <c r="F102">
-        <v>-0.1251696339090438</v>
+        <v>-0.8022799306433487</v>
       </c>
       <c r="G102">
-        <v>-7.082039347916671</v>
+        <v>-5.778353135642756</v>
       </c>
     </row>
   </sheetData>
